--- a/output/pdf_financials_xlsx/NWC.xlsx
+++ b/output/pdf_financials_xlsx/NWC.xlsx
@@ -7918,13 +7918,13 @@
         <v>30.418</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>19.867</v>
+        <v>32.785</v>
       </c>
       <c r="M91" s="3" t="n">
         <v>-0.265</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>20.132</v>
+        <v>33.05</v>
       </c>
       <c r="O91" s="3" t="n">
         <v>20.315</v>
@@ -8001,13 +8001,13 @@
         <v>2.62</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>3.53</v>
+        <v>6.1</v>
       </c>
       <c r="M92" s="3" t="n">
         <v>2.57</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>3.53</v>
+        <v>6.1</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>8.65</v>

--- a/output/pdf_financials_xlsx/NWC.xlsx
+++ b/output/pdf_financials_xlsx/NWC.xlsx
@@ -3121,34 +3121,34 @@
         <v>0</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>29.129</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>37.243</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>30.243</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>25.16</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>28.187</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>71.536</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>58.809</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>53.359</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>0</v>
@@ -3287,34 +3287,34 @@
         <v>0</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>29.129</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>37.243</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>30.243</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>25.16</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>28.187</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>71.536</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>58.809</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>53.359</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>0</v>
@@ -4283,34 +4283,34 @@
         <v>315.84</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>58.263</v>
+        <v>29.134</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>36.829</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>84.149</v>
+        <v>53.906</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>73.45999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>399.593</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>43.951</v>
+        <v>15.764</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>84.953</v>
+        <v>13.417</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>474.844</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>95.27200000000001</v>
+        <v>36.463</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>115.248</v>
+        <v>61.889</v>
       </c>
       <c r="T48" s="3" t="n">
         <v>556.9880000000001</v>
@@ -16894,7 +16894,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -73236,7 +73236,7 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">

--- a/output/pdf_financials_xlsx/NWC.xlsx
+++ b/output/pdf_financials_xlsx/NWC.xlsx
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>1.343</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>1.101</v>
       </c>
       <c r="I112" s="1" t="inlineStr">
         <is>
@@ -9587,34 +9587,34 @@
         </is>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>2.017</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="N112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.705</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>3.038</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="S112" s="3" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="T112" s="1" t="inlineStr">
         <is>
@@ -10762,25 +10762,25 @@
         <v>0</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>0</v>
+        <v>-2.482</v>
       </c>
       <c r="N126" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O126" s="3" t="n">
-        <v>0</v>
+        <v>-3.427</v>
       </c>
       <c r="P126" s="3" t="n">
-        <v>0</v>
+        <v>-2.214</v>
       </c>
       <c r="Q126" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R126" s="3" t="n">
-        <v>0</v>
+        <v>-2.521</v>
       </c>
       <c r="S126" s="3" t="n">
-        <v>0</v>
+        <v>-2.593</v>
       </c>
       <c r="T126" s="1" t="inlineStr">
         <is>
@@ -35628,7 +35628,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -36386,7 +36390,11 @@
           <t>Dividends to non-controlling interests (Note 20)</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -38244,7 +38252,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -45412,7 +45424,11 @@
           <t>Dividends to non-controlling interests (Note 19)</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -47826,7 +47842,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NWC.xlsx
+++ b/output/pdf_financials_xlsx/NWC.xlsx
@@ -1208,16 +1208,16 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>464.218</v>
+        <v>97.46599999999999</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>522.614</v>
+        <v>107.321</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>541.497</v>
+        <v>118.131</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>586.086</v>
+        <v>113.971</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
@@ -1225,25 +1225,21 @@
         </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0</v>
+        <v>77376</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>153328</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>195897</v>
       </c>
       <c r="R11" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S11" s="3" t="n">
+        <v>180305</v>
       </c>
       <c r="T11" s="1" t="inlineStr">
         <is>
@@ -3382,7 +3378,7 @@
         <v>80.765</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0</v>
+        <v>22.412</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>104.869</v>
@@ -3714,7 +3710,7 @@
         <v>80.765</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0</v>
+        <v>22.412</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>104.869</v>
@@ -4295,7 +4291,7 @@
         <v>48.3</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>399.593</v>
+        <v>377.181</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>15.764</v>
@@ -10504,16 +10500,16 @@
         </is>
       </c>
       <c r="J123" s="3" t="n">
-        <v>0</v>
+        <v>78.572</v>
       </c>
       <c r="K123" s="3" t="n">
-        <v>0</v>
+        <v>13.081</v>
       </c>
       <c r="L123" s="3" t="n">
-        <v>0</v>
+        <v>11.567</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>0</v>
+        <v>-9.092000000000001</v>
       </c>
       <c r="N123" s="3" t="n">
         <v>0</v>
@@ -10525,13 +10521,13 @@
         <v>0</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>0</v>
+        <v>44.071</v>
       </c>
       <c r="R123" s="3" t="n">
-        <v>0</v>
+        <v>49.436</v>
       </c>
       <c r="S123" s="3" t="n">
-        <v>0</v>
+        <v>-8.891</v>
       </c>
       <c r="T123" s="1" t="inlineStr">
         <is>
@@ -10670,16 +10666,16 @@
         </is>
       </c>
       <c r="J125" s="3" t="n">
-        <v>-75.95</v>
+        <v>2.622</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>13.081</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>11.567</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-9.092000000000001</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>0</v>
@@ -10691,13 +10687,13 @@
         <v>0</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>44.071</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>49.436</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-8.891</v>
       </c>
       <c r="T125" s="1" t="inlineStr">
         <is>
@@ -13802,7 +13798,11 @@
           <t>Other assets, intangible assets and goodwill</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -29274,7 +29274,11 @@
           <t>Other assets, intangible assets and goodwill</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -35952,7 +35956,11 @@
           <t>Net (decrease)/increase in long-term debt (Note 12)</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -37912,7 +37920,11 @@
           <t>Net increase in long-term debt (Note 12)</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -45200,7 +45212,11 @@
           <t>Net (decrease)/increase in long-term debt (Note 11)</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -45886,7 +45902,11 @@
           <t>Increase in long-term debt (Note 11)</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -46802,7 +46822,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -49688,7 +49712,11 @@
           <t>Earnings from operations $ 60,741 $ 51,697 $ 47,824 $ 209,546 $</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -50504,7 +50532,11 @@
           <t>Earnings from operations $ 43,865 $ 37,166 $ 33,417 $ 146,875 $</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -51204,7 +51236,11 @@
           <t>Earnings from operations $ 11,893 $ 10,755 $ 10,630 $ 45,496 $</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -58990,7 +59026,11 @@
           <t>Earnings from operations $ 33,417 $ 36,276 $ 17,642 $</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
@@ -59676,7 +59716,11 @@
           <t>Earnings from operations $ 10,630 $ 10,456 $ 6,939 $</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
           <t>-</t>
@@ -60364,7 +60408,11 @@
           <t>Earnings from operations $ 47,824 $ 49,588 $ 26,734 $</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
@@ -73148,7 +73196,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
           <t>-</t>
